--- a/data/satisfaction_detail/2026/1-8月/会展服务商.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/会展服务商.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.82</v>
+        <v>9.900705543556514</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.923153347732182</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.967876169906408</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.94</v>
+        <v>9.94889848812095</v>
       </c>
     </row>
     <row r="4">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.93</v>
+        <v>9.962303815694746</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.75</v>
+        <v>9.734312455003598</v>
       </c>
     </row>
     <row r="7">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.68</v>
+        <v>9.776457883369332</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.981857451403886</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.977254561251087</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.92</v>
+        <v>9.954509122502172</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.91</v>
+        <v>9.936750651607298</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.93</v>
+        <v>9.926565874730022</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.914326853851692</v>
       </c>
     </row>
     <row r="13">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.981151907847371</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>10</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.93</v>
+        <v>9.963009359251261</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.981151907847371</v>
       </c>
     </row>
     <row r="16">
@@ -657,7 +657,7 @@
         <v>10</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.77</v>
+        <v>9.886609071274298</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9.720000000000001</v>
+        <v>9.810439164866811</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>9.93</v>
+        <v>9.949496040316774</v>
       </c>
     </row>
     <row r="18">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.93</v>
+        <v>9.9451403887689</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>10</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.887516198704104</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>10</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>9.75</v>
+        <v>9.868567314614831</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>10</v>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.75</v>
+        <v>9.85069834413247</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>10</v>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.757336213102951</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>10</v>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.981857451403886</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.92</v>
+        <v>9.9622030237581</v>
       </c>
     </row>
     <row r="24">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.5</v>
+        <v>9.707544996400287</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>9.5</v>
+        <v>9.640014398848091</v>
       </c>
     </row>
     <row r="25">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.5</v>
+        <v>9.482447804175667</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>10</v>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9.93</v>
+        <v>9.956155507559396</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>9.94</v>
+        <v>9.939928005759539</v>
       </c>
     </row>
     <row r="27">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>9.77</v>
+        <v>9.886609071274298</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>9.92</v>
+        <v>9.914326853851692</v>
       </c>
     </row>
     <row r="28">
@@ -826,7 +826,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>9.93</v>
+        <v>9.962303815694746</v>
       </c>
     </row>
     <row r="30">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.981857451403886</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.943354931605471</v>
       </c>
     </row>
     <row r="31">
